--- a/data/agricultural_facilities_list/data.xlsx
+++ b/data/agricultural_facilities_list/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -719,19 +719,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="str">
-        <v>34.241482</v>
+        <v>34.233962</v>
       </c>
       <c r="C7" t="str">
-        <v>133.999299</v>
+        <v>134.010987</v>
       </c>
       <c r="D7" t="str">
-        <v>高松市香南町西庄集会所</v>
+        <v>高松市香南町原集会所</v>
       </c>
       <c r="E7" t="str">
-        <v>高松市香南町西庄1203番地１</v>
+        <v>高松市香南町由佐1687番地１</v>
       </c>
       <c r="F7" t="str">
         <v>087-839-2422</v>
@@ -749,19 +749,19 @@
         <v>集会室</v>
       </c>
       <c r="K7" t="str">
-        <v>54㎡</v>
+        <v>49.5㎡</v>
       </c>
       <c r="L7" t="str">
         <v>調理室</v>
       </c>
       <c r="M7" t="str">
-        <v>23㎡</v>
+        <v>18.35㎡</v>
       </c>
       <c r="N7" t="str">
-        <v>和室</v>
+        <v/>
       </c>
       <c r="O7" t="str">
-        <v>16㎡</v>
+        <v/>
       </c>
       <c r="P7" t="str">
         <v/>
@@ -772,19 +772,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="str">
-        <v>34.233962</v>
+        <v>34.246112</v>
       </c>
       <c r="C8" t="str">
-        <v>134.010987</v>
+        <v>134.008962</v>
       </c>
       <c r="D8" t="str">
-        <v>高松市香南町原集会所</v>
+        <v>高松市香南町横井集会所</v>
       </c>
       <c r="E8" t="str">
-        <v>高松市香南町由佐1687番地１</v>
+        <v>高松市香南町横井388番地１</v>
       </c>
       <c r="F8" t="str">
         <v>087-839-2422</v>
@@ -802,19 +802,19 @@
         <v>集会室</v>
       </c>
       <c r="K8" t="str">
-        <v>49.5㎡</v>
+        <v>59.3㎡</v>
       </c>
       <c r="L8" t="str">
         <v>調理室</v>
       </c>
       <c r="M8" t="str">
-        <v>18.35㎡</v>
+        <v>23.6㎡</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>和室</v>
       </c>
       <c r="O8" t="str">
-        <v/>
+        <v>18.76㎡</v>
       </c>
       <c r="P8" t="str">
         <v/>
@@ -825,19 +825,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="str">
-        <v>34.246112</v>
+        <v>34.255252</v>
       </c>
       <c r="C9" t="str">
-        <v>134.008962</v>
+        <v>134.013184</v>
       </c>
       <c r="D9" t="str">
-        <v>高松市香南町横井集会所</v>
+        <v>高松市香南町吉光研修センター</v>
       </c>
       <c r="E9" t="str">
-        <v>高松市香南町横井388番地１</v>
+        <v>高松市香南町吉光159番地</v>
       </c>
       <c r="F9" t="str">
         <v>087-839-2422</v>
@@ -855,19 +855,19 @@
         <v>集会室</v>
       </c>
       <c r="K9" t="str">
-        <v>59.3㎡</v>
+        <v>56.81㎡</v>
       </c>
       <c r="L9" t="str">
         <v>調理室</v>
       </c>
       <c r="M9" t="str">
-        <v>23.6㎡</v>
+        <v>21.66㎡</v>
       </c>
       <c r="N9" t="str">
         <v>和室</v>
       </c>
       <c r="O9" t="str">
-        <v>18.76㎡</v>
+        <v>18.62㎡</v>
       </c>
       <c r="P9" t="str">
         <v/>
@@ -878,72 +878,72 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="str">
-        <v>34.255252</v>
+        <v>34.245211</v>
       </c>
       <c r="C10" t="str">
-        <v>134.013184</v>
+        <v>134.00037</v>
       </c>
       <c r="D10" t="str">
-        <v>高松市香南町吉光研修センター</v>
+        <v>高松市香南町池西農村環境改善センター</v>
       </c>
       <c r="E10" t="str">
-        <v>高松市香南町吉光159番地</v>
+        <v>高松市香南町池内522番地1</v>
       </c>
       <c r="F10" t="str">
         <v>087-839-2422</v>
       </c>
       <c r="G10" t="str">
-        <v>08:00</v>
+        <v>09:00</v>
       </c>
       <c r="H10" t="str">
-        <v>21:00</v>
+        <v>22:00</v>
       </c>
       <c r="I10" t="str">
         <v>月曜日、祝日、年末年始</v>
       </c>
       <c r="J10" t="str">
-        <v>集会室</v>
+        <v>多目的ホール</v>
       </c>
       <c r="K10" t="str">
-        <v>56.81㎡</v>
+        <v>192㎡</v>
       </c>
       <c r="L10" t="str">
-        <v>調理室</v>
+        <v>和室会議室</v>
       </c>
       <c r="M10" t="str">
-        <v>21.66㎡</v>
+        <v>63㎡</v>
       </c>
       <c r="N10" t="str">
-        <v>和室</v>
+        <v>調理実習室</v>
       </c>
       <c r="O10" t="str">
-        <v>18.62㎡</v>
+        <v>54㎡</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>農事研修室</v>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>99㎡</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="str">
-        <v>34.245211</v>
+        <v>34.240298</v>
       </c>
       <c r="C11" t="str">
-        <v>134.00037</v>
+        <v>134.018974</v>
       </c>
       <c r="D11" t="str">
-        <v>高松市香南町池西農村環境改善センター</v>
+        <v>高松市香南町由佐農村環境改善センター</v>
       </c>
       <c r="E11" t="str">
-        <v>高松市香南町池内522番地1</v>
+        <v>高松市香南町由佐357番地2</v>
       </c>
       <c r="F11" t="str">
         <v>087-839-2422</v>
@@ -961,83 +961,30 @@
         <v>多目的ホール</v>
       </c>
       <c r="K11" t="str">
-        <v>192㎡</v>
+        <v>218.48㎡</v>
       </c>
       <c r="L11" t="str">
-        <v>和室会議室</v>
+        <v>第1研修室</v>
       </c>
       <c r="M11" t="str">
-        <v>63㎡</v>
+        <v>53.81㎡</v>
       </c>
       <c r="N11" t="str">
+        <v>第2研修室</v>
+      </c>
+      <c r="O11" t="str">
+        <v>53.82㎡</v>
+      </c>
+      <c r="P11" t="str">
         <v>調理実習室</v>
       </c>
-      <c r="O11" t="str">
-        <v>54㎡</v>
-      </c>
-      <c r="P11" t="str">
-        <v>農事研修室</v>
-      </c>
       <c r="Q11" t="str">
-        <v>99㎡</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>34.240298</v>
-      </c>
-      <c r="C12" t="str">
-        <v>134.018974</v>
-      </c>
-      <c r="D12" t="str">
-        <v>高松市香南町由佐農村環境改善センター</v>
-      </c>
-      <c r="E12" t="str">
-        <v>高松市香南町由佐357番地2</v>
-      </c>
-      <c r="F12" t="str">
-        <v>087-839-2422</v>
-      </c>
-      <c r="G12" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="H12" t="str">
-        <v>22:00</v>
-      </c>
-      <c r="I12" t="str">
-        <v>月曜日、祝日、年末年始</v>
-      </c>
-      <c r="J12" t="str">
-        <v>多目的ホール</v>
-      </c>
-      <c r="K12" t="str">
-        <v>218.48㎡</v>
-      </c>
-      <c r="L12" t="str">
-        <v>第1研修室</v>
-      </c>
-      <c r="M12" t="str">
-        <v>53.81㎡</v>
-      </c>
-      <c r="N12" t="str">
-        <v>第2研修室</v>
-      </c>
-      <c r="O12" t="str">
-        <v>53.82㎡</v>
-      </c>
-      <c r="P12" t="str">
-        <v>調理実習室</v>
-      </c>
-      <c r="Q12" t="str">
         <v>59.42㎡</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q11"/>
   </ignoredErrors>
 </worksheet>
 </file>